--- a/Squeeze_Project_Donations_v2.xlsx
+++ b/Squeeze_Project_Donations_v2.xlsx
@@ -1509,7 +1509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2068,40 +2068,63 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="n"/>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>Mar 25</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>Stacey Selenfriend</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>Venmo</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="n"/>
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C27" s="9">
+      <c r="C28" s="9">
         <f>SUM(C5:C25)</f>
         <v/>
       </c>
-      <c r="D27" s="8" t="n"/>
-      <c r="E27" s="10">
+      <c r="D28" s="8" t="n"/>
+      <c r="E28" s="10">
         <f>SUM(E5:E25)</f>
         <v/>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="15" t="inlineStr">
+    <row r="29">
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>Est. Fees</t>
         </is>
       </c>
-      <c r="C28" s="16">
+      <c r="C29" s="16">
         <f>-E26</f>
         <v/>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="17" t="inlineStr">
+    <row r="30">
+      <c r="B30" s="17" t="inlineStr">
         <is>
           <t>Net Received</t>
         </is>
       </c>
-      <c r="C29" s="18">
+      <c r="C30" s="18">
         <f>C26+C27</f>
         <v/>
       </c>

--- a/Squeeze_Project_Donations_v2.xlsx
+++ b/Squeeze_Project_Donations_v2.xlsx
@@ -756,7 +756,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1533,7 +1532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1557,6 +1556,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2114,40 +2114,63 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="n"/>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>Mar 25</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>Kelly Hershkowitz</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="E28" s="14" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="n"/>
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C28" s="9">
+      <c r="C29" s="9">
         <f>SUM(C5:C25)</f>
         <v/>
       </c>
-      <c r="D28" s="8" t="n"/>
-      <c r="E28" s="10">
+      <c r="D29" s="8" t="n"/>
+      <c r="E29" s="10">
         <f>SUM(E5:E25)</f>
         <v/>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="15" t="inlineStr">
+    <row r="30">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>Est. Fees</t>
         </is>
       </c>
-      <c r="C29" s="16">
+      <c r="C30" s="16">
         <f>-E26</f>
         <v/>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="17" t="inlineStr">
+    <row r="31">
+      <c r="B31" s="17" t="inlineStr">
         <is>
           <t>Net Received</t>
         </is>
       </c>
-      <c r="C30" s="18">
+      <c r="C31" s="18">
         <f>C26+C27</f>
         <v/>
       </c>
